--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -285,7 +285,7 @@
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Phaenotypisierung</t>
+    <t>anamneseUndDiagnostik.phaenotypisierung</t>
   </si>
   <si>
     <t>Event</t>
@@ -644,7 +644,7 @@
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/ValueSet/mii-vs-seltene-hpo-phenotypic-observation-codes</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Phaenotypisierung.HPOTerm</t>
+    <t>anamneseUndDiagnostik.phaenotypisierung.hpoTerm</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -764,7 +764,7 @@
     <t>Coding.version</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Phaenotypisierung.HPOVersion</t>
+    <t>anamneseUndDiagnostik.phaenotypisierung.hpoVersion</t>
   </si>
   <si>
     <t>C*E.7</t>
@@ -922,7 +922,7 @@
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Untersuchungsdatum</t>
+    <t>anamneseUndDiagnostik.untersuchungsdatum</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -986,7 +986,7 @@
     <t>Clinically relevant time/time-period for observation</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Phaenotypisierung.ZeitraumSymptom.ZeitraumSymptom</t>
+    <t>anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.zeitraumSymptom</t>
   </si>
   <si>
     <t>Observation.effective[x]:effectivePeriod</t>
@@ -1267,7 +1267,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.MethodeDiagnosestellung</t>
+    <t>anamneseUndDiagnostik.methodeDiagnosestellung</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1656,7 +1656,7 @@
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/ValueSet/mii-vs-seltene-hpo-presence-status</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Phaenotypisierung.HPOStatus</t>
+    <t>anamneseUndDiagnostik.phaenotypisierung.hpoStatus</t>
   </si>
   <si>
     <t>Observation.component:status.dataAbsentReason</t>
@@ -1674,7 +1674,7 @@
     <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/ValueSet/mii-vs-seltene-symptom-change-status-combined</t>
   </si>
   <si>
-    <t>AnamneseUndDiagnostik.Phaenotypisierung.VerlaufSymptom</t>
+    <t>anamneseUndDiagnostik.phaenotypisierung.verlaufSymptom</t>
   </si>
   <si>
     <t>Observation.component:status.interpretation.id</t>
@@ -2149,7 +2149,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="66.46875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="65.90625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -871,7 +871,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>Patient</t>
+    <t>persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-hpo-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
